--- a/output/graficos_regionales/plot_regional_serie_i_ingr_m_2020_atacama.xlsx
+++ b/output/graficos_regionales/plot_regional_serie_i_ingr_m_2020_atacama.xlsx
@@ -288,7 +288,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 16:35</t>
+    <t xml:space="preserve">2026-10-05 01:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -726,7 +726,7 @@
         <v>887371.94</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>804762.62</v>
+        <v>804762.63</v>
       </c>
     </row>
     <row r="5">
@@ -737,7 +737,7 @@
         <v>892172.44</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>799364.12</v>
+        <v>799364.13</v>
       </c>
     </row>
     <row r="6">
@@ -836,7 +836,7 @@
         <v>928520.94</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>826816.62</v>
+        <v>826816.63</v>
       </c>
     </row>
     <row r="15">
@@ -913,7 +913,7 @@
         <v>909520.56</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>849932.62</v>
+        <v>849932.63</v>
       </c>
     </row>
     <row r="22">
@@ -1001,7 +1001,7 @@
         <v>977106.56</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>885489.12</v>
+        <v>885489.13</v>
       </c>
     </row>
     <row r="30">
@@ -1012,7 +1012,7 @@
         <v>968813.25</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>873830.12</v>
+        <v>873830.13</v>
       </c>
     </row>
     <row r="31">
@@ -1086,7 +1086,7 @@
         <v>38</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>1078438.12</v>
+        <v>1078438.13</v>
       </c>
       <c r="C37" s="2" t="n">
         <v>969716.44</v>
@@ -1163,10 +1163,10 @@
         <v>45</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>1054201.62</v>
+        <v>1054201.63</v>
       </c>
       <c r="C44" s="2" t="n">
-        <v>953641.12</v>
+        <v>953641.13</v>
       </c>
     </row>
     <row r="45">
@@ -1284,10 +1284,10 @@
         <v>56</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>1137791.12</v>
+        <v>1137791.13</v>
       </c>
       <c r="C55" s="2" t="n">
-        <v>1048559.62</v>
+        <v>1048559.63</v>
       </c>
     </row>
     <row r="56">
@@ -1298,7 +1298,7 @@
         <v>1165753.25</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>1059287.62</v>
+        <v>1059287.63</v>
       </c>
     </row>
     <row r="57">
@@ -1339,10 +1339,10 @@
         <v>61</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>1200187.12</v>
+        <v>1200187.13</v>
       </c>
       <c r="C60" s="2" t="n">
-        <v>1093564.62</v>
+        <v>1093564.63</v>
       </c>
     </row>
     <row r="61">
@@ -1350,7 +1350,7 @@
         <v>62</v>
       </c>
       <c r="B61" s="2" t="n">
-        <v>1319618.12</v>
+        <v>1319618.13</v>
       </c>
       <c r="C61" s="2" t="n">
         <v>1183065.88</v>
@@ -1364,7 +1364,7 @@
         <v>1301777.38</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>1145616.62</v>
+        <v>1145616.63</v>
       </c>
     </row>
     <row r="63">
@@ -1383,7 +1383,7 @@
         <v>65</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>1265800.62</v>
+        <v>1265800.63</v>
       </c>
       <c r="C64" s="2" t="n">
         <v>1158414.88</v>
@@ -1419,7 +1419,7 @@
         <v>1289239.75</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>1184430.62</v>
+        <v>1184430.63</v>
       </c>
     </row>
     <row r="68">
@@ -1449,7 +1449,7 @@
         <v>71</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>1380575.62</v>
+        <v>1380575.63</v>
       </c>
       <c r="C70" s="2" t="n">
         <v>1246393.5</v>
@@ -1504,7 +1504,7 @@
         <v>76</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>1305857.12</v>
+        <v>1305857.13</v>
       </c>
       <c r="C75" s="2" t="n">
         <v>1214165.25</v>
@@ -1518,7 +1518,7 @@
         <v>1352332.25</v>
       </c>
       <c r="C76" s="2" t="n">
-        <v>1240434.12</v>
+        <v>1240434.13</v>
       </c>
     </row>
     <row r="77">
@@ -1551,7 +1551,7 @@
         <v>1351226.88</v>
       </c>
       <c r="C79" s="2" t="n">
-        <v>1253268.12</v>
+        <v>1253268.13</v>
       </c>
     </row>
     <row r="80">
@@ -1562,7 +1562,7 @@
         <v>1386195.88</v>
       </c>
       <c r="C80" s="2" t="n">
-        <v>1274861.62</v>
+        <v>1274861.63</v>
       </c>
     </row>
     <row r="81">
@@ -1584,7 +1584,7 @@
         <v>1459725</v>
       </c>
       <c r="C82" s="2" t="n">
-        <v>1327655.12</v>
+        <v>1327655.13</v>
       </c>
     </row>
     <row r="83">
